--- a/AAII_Financials/Yearly/ISDAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ISDAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>ISDAY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,82 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4194100</v>
+      </c>
+      <c r="E8" s="3">
         <v>4046300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3565400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3595800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2546700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2598100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2269100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2236100</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -756,36 +762,42 @@
       <c r="J9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4194100</v>
+      </c>
+      <c r="E10" s="3">
         <v>4046300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3565400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3595800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2546700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2598100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2269100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2236100</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -797,8 +809,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -823,9 +836,12 @@
       <c r="J12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -850,63 +866,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E14" s="3">
         <v>3300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>10000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E15" s="3">
         <v>60800</v>
       </c>
-      <c r="E15" s="3">
-        <v>57700</v>
-      </c>
       <c r="F15" s="3">
+        <v>164700</v>
+      </c>
+      <c r="G15" s="3">
         <v>173000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>152700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>134900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>113500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>124800</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -915,62 +940,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2285400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2208600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2051000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2203600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2068200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1821900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1643500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1641000</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1908700</v>
+      </c>
+      <c r="E18" s="3">
         <v>1837700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1514400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1392100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>478400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>776200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>625600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>595100</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -982,62 +1014,69 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E20" s="3">
         <v>3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-15600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1987800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1895400</v>
       </c>
-      <c r="E21" s="3">
-        <v>1579800</v>
-      </c>
       <c r="F21" s="3">
+        <v>1686700</v>
+      </c>
+      <c r="G21" s="3">
         <v>1571600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>646700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>915700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>740700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>720200</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1062,63 +1101,72 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1916400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1831300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1520600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1397300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>484000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>779100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>625600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>595400</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>721800</v>
+      </c>
+      <c r="E24" s="3">
         <v>643100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>513600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>487400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>170800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>269800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>211100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>215300</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1143,63 +1191,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1194600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1188200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1007000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>909900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>313200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>509200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>414500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>380100</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1175400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1164000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>993900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>891500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>303300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>492800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>402700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>362800</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1224,9 +1281,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1251,9 +1311,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1278,9 +1341,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1305,63 +1371,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>15600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1175400</v>
+      </c>
+      <c r="E33" s="3">
         <v>1164000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>993900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>891600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>303300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>492700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>402700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>362800</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1386,68 +1461,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1175400</v>
+      </c>
+      <c r="E35" s="3">
         <v>1164000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>993900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>891600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>303300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>492700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>402700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>362800</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1459,8 +1543,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1472,89 +1557,99 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13513200</v>
+        <v>15668700</v>
       </c>
       <c r="E41" s="3">
+        <v>11167400</v>
+      </c>
+      <c r="F41" s="3">
         <v>18305600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18980500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13099400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7437200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5739100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7976600</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5613500</v>
+        <v>7244300</v>
       </c>
       <c r="E42" s="3">
+        <v>7473100</v>
+      </c>
+      <c r="F42" s="3">
         <v>4282900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2611300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2887300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2259900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1970500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1621400</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>237800</v>
+      </c>
+      <c r="E43" s="3">
         <v>316300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>178300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>218000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>143100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>168500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>144000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>139500</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1579,144 +1674,162 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E45" s="3">
         <v>134400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>90200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>169800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>227400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>250400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>206300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>188800</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>20250500</v>
+        <v>23680100</v>
       </c>
       <c r="E46" s="3">
+        <v>19764300</v>
+      </c>
+      <c r="F46" s="3">
         <v>23220700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22165400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16495900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10172500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8086800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9950400</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15629700</v>
+      </c>
+      <c r="E47" s="3">
         <v>14439000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12216800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13921200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13063300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10264000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9575900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9049500</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1226100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1154600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1095800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>955900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>801900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>465500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>125800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>460000</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>480200</v>
+      </c>
+      <c r="E49" s="3">
         <v>463200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>403300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>438500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>424900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>328000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>272900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>268000</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1741,9 +1854,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1768,36 +1884,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>252000</v>
+      </c>
+      <c r="E52" s="3">
         <v>250700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>252000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>273900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>196600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>197700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>492600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>228800</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1822,36 +1944,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>119852800</v>
+      </c>
+      <c r="E54" s="3">
         <v>109883700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>107145000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>107734900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>91442400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>75221600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>63998700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>63754300</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1863,8 +1991,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1876,170 +2005,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>93190300</v>
+      </c>
+      <c r="E57" s="3">
         <v>85769000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>87493100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>87974800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>74440700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>60195700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>52422900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>51888000</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6457400</v>
+        <v>6369100</v>
       </c>
       <c r="E58" s="3">
+        <v>6437400</v>
+      </c>
+      <c r="F58" s="3">
         <v>3761900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2071500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2375000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1501100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1170700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1491400</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3575200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3008900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3055500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3218000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2955700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2517000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1955700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1956300</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>95653000</v>
+        <v>103551600</v>
       </c>
       <c r="E60" s="3">
+        <v>95633000</v>
+      </c>
+      <c r="F60" s="3">
         <v>94676800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>93738200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>80184800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>64515800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55799500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55571300</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4597000</v>
+        <v>5860000</v>
       </c>
       <c r="E61" s="3">
+        <v>4616900</v>
+      </c>
+      <c r="F61" s="3">
         <v>3818800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5054800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3381900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3801000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2268000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2201500</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>744900</v>
+      </c>
+      <c r="E62" s="3">
         <v>840000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>711300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>886400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>766500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1087400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>991900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1077600</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2064,9 +2212,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2091,9 +2242,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2118,36 +2272,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>110769300</v>
+      </c>
+      <c r="E66" s="3">
         <v>101764900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>99899300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>100614100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>85306100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>69665000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>59270800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>59123600</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2159,8 +2319,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2185,9 +2346,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2212,9 +2376,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2239,9 +2406,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2266,36 +2436,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7314100</v>
+      </c>
+      <c r="E72" s="3">
         <v>6528800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5798100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5674400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4672100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4080400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3384100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3241000</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2320,9 +2496,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2347,9 +2526,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2374,36 +2556,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8667300</v>
+      </c>
+      <c r="E76" s="3">
         <v>7906600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7075600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6907100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5966800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5407500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4589300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4494100</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2428,68 +2616,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1175400</v>
+      </c>
+      <c r="E81" s="3">
         <v>1164000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>993900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>891600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>303300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>492700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>402700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>362800</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2501,35 +2698,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E83" s="3">
         <v>60800</v>
       </c>
-      <c r="E83" s="3">
-        <v>57700</v>
-      </c>
       <c r="F83" s="3">
+        <v>164700</v>
+      </c>
+      <c r="G83" s="3">
         <v>173000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>152700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>134900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>113500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>124800</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2554,9 +2755,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2581,9 +2785,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2608,9 +2815,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2635,9 +2845,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2662,36 +2875,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1162200</v>
+      </c>
+      <c r="E89" s="3">
         <v>559000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-269000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1433000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2193900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1664100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>39100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1671800</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2703,35 +2922,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-229500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-331500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-302600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-314100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-260000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-171400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-126600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-150100</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2756,9 +2979,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2783,36 +3009,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8136800</v>
+        <v>-7333000</v>
       </c>
       <c r="E94" s="3">
-        <v>-7805400</v>
+        <v>-8347800</v>
       </c>
       <c r="F94" s="3">
+        <v>-8036000</v>
+      </c>
+      <c r="G94" s="3">
         <v>-8199500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5959300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2795800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5961400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1959400</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2824,35 +3056,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>316600</v>
+      </c>
+      <c r="E96" s="3">
         <v>290700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>175500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>46300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>15200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>73800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>31600</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2877,9 +3113,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2904,9 +3143,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2931,88 +3173,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9830600</v>
+      </c>
+      <c r="E100" s="3">
         <v>3519600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9581900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12303000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8972300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2423200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4207400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-28200</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-11400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>191700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-66900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-78100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-67500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>52400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>11200</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-4069600</v>
+        <v>3634000</v>
       </c>
       <c r="E102" s="3">
-        <v>1699200</v>
+        <v>-4280700</v>
       </c>
       <c r="F102" s="3">
+        <v>1468600</v>
+      </c>
+      <c r="G102" s="3">
         <v>5469600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5128800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1224100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1662500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-304600</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ISDAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ISDAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>ISDAY</t>
   </si>
@@ -656,88 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4194100</v>
+        <v>4035100</v>
       </c>
       <c r="E8" s="3">
-        <v>4046300</v>
+        <v>3511200</v>
       </c>
       <c r="F8" s="3">
+        <v>3369900</v>
+      </c>
+      <c r="G8" s="3">
         <v>3565400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3595800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2546700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2598100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2269100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2236100</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -765,39 +771,45 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>4194100</v>
+        <v>4035100</v>
       </c>
       <c r="E10" s="3">
-        <v>4046300</v>
+        <v>3511200</v>
       </c>
       <c r="F10" s="3">
+        <v>3369900</v>
+      </c>
+      <c r="G10" s="3">
         <v>3565400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3595800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2546700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2598100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2269100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2236100</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +822,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,69 +885,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E14" s="3">
         <v>1400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>70000</v>
+        <v>98500</v>
       </c>
       <c r="E15" s="3">
-        <v>60800</v>
+        <v>101600</v>
       </c>
       <c r="F15" s="3">
+        <v>173000</v>
+      </c>
+      <c r="G15" s="3">
         <v>164700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>173000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>152700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>134900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>113500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>124800</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2285400</v>
+        <v>2048600</v>
       </c>
       <c r="E17" s="3">
-        <v>2208600</v>
+        <v>1701900</v>
       </c>
       <c r="F17" s="3">
+        <v>1697400</v>
+      </c>
+      <c r="G17" s="3">
         <v>2051000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2203600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2068200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1821900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1643500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1641000</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1908700</v>
+        <v>1986500</v>
       </c>
       <c r="E18" s="3">
-        <v>1837700</v>
+        <v>1809300</v>
       </c>
       <c r="F18" s="3">
+        <v>1672500</v>
+      </c>
+      <c r="G18" s="3">
         <v>1514400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1392100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>478400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>776200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>625600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>595100</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,68 +1047,75 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9100</v>
       </c>
-      <c r="E20" s="3">
-        <v>3100</v>
-      </c>
       <c r="F20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G20" s="3">
         <v>-7700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-15600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1987800</v>
+        <v>2099100</v>
       </c>
       <c r="E21" s="3">
-        <v>1895400</v>
+        <v>1919900</v>
       </c>
       <c r="F21" s="3">
+        <v>1841800</v>
+      </c>
+      <c r="G21" s="3">
         <v>1686700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1571600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>646700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>915700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>740700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>720200</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1104,69 +1143,78 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1916400</v>
+        <v>1992800</v>
       </c>
       <c r="E23" s="3">
-        <v>1831300</v>
+        <v>1817000</v>
       </c>
       <c r="F23" s="3">
+        <v>1665500</v>
+      </c>
+      <c r="G23" s="3">
         <v>1520600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1397300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>484000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>779100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>625600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>595400</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>721800</v>
+        <v>730600</v>
       </c>
       <c r="E24" s="3">
-        <v>643100</v>
+        <v>696800</v>
       </c>
       <c r="F24" s="3">
+        <v>602000</v>
+      </c>
+      <c r="G24" s="3">
         <v>513600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>487400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>170800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>269800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>211100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>215300</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1194600</v>
+        <v>1262200</v>
       </c>
       <c r="E26" s="3">
-        <v>1188200</v>
+        <v>1120200</v>
       </c>
       <c r="F26" s="3">
+        <v>1063500</v>
+      </c>
+      <c r="G26" s="3">
         <v>1007000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>909900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>313200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>509200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>414500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>380100</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1298600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1175400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1164000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>993900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>891500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>303300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>492800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>402700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>362800</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,20 +1341,23 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>43300</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>51100</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>89700</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,69 +1440,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E32" s="3">
         <v>9100</v>
       </c>
-      <c r="E32" s="3">
-        <v>-3100</v>
-      </c>
       <c r="F32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G32" s="3">
         <v>7700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>15600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1298600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1175400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1164000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>993900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>891600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>303300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>492700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>402700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>362800</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1298600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1175400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1164000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>993900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>891600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>303300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>492700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>402700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>362800</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,98 +1643,108 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18226500</v>
+      </c>
+      <c r="E41" s="3">
         <v>15668700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11167400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18305600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18980500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13099400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7437200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5739100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7976600</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>7244300</v>
+        <v>10323100</v>
       </c>
       <c r="E42" s="3">
+        <v>7241000</v>
+      </c>
+      <c r="F42" s="3">
         <v>7473100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4282900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2611300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2887300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2259900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1970500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1621400</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>237800</v>
+        <v>206100</v>
       </c>
       <c r="E43" s="3">
+        <v>221000</v>
+      </c>
+      <c r="F43" s="3">
         <v>316300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>178300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>218000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>143100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>168500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>144000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>139500</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1677,159 +1772,177 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>125200</v>
+        <v>7360700</v>
       </c>
       <c r="E45" s="3">
+        <v>6183200</v>
+      </c>
+      <c r="F45" s="3">
         <v>134400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>90200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>169800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>227400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>250400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>206300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>188800</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>23680100</v>
+        <v>36463900</v>
       </c>
       <c r="E46" s="3">
+        <v>29672200</v>
+      </c>
+      <c r="F46" s="3">
         <v>19764300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23220700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22165400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16495900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10172500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8086800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9950400</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>15629700</v>
+        <v>19989600</v>
       </c>
       <c r="E47" s="3">
+        <v>15626700</v>
+      </c>
+      <c r="F47" s="3">
         <v>14439000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12216800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13921200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13063300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10264000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9575900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9049500</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1226100</v>
+        <v>1192600</v>
       </c>
       <c r="E48" s="3">
+        <v>1092400</v>
+      </c>
+      <c r="F48" s="3">
         <v>1154600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1095800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>955900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>801900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>465500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>125800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>460000</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>480200</v>
+        <v>379900</v>
       </c>
       <c r="E49" s="3">
+        <v>326400</v>
+      </c>
+      <c r="F49" s="3">
         <v>463200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>403300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>438500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>424900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>328000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>272900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>268000</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,39 +2003,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>263200</v>
+      </c>
+      <c r="E52" s="3">
         <v>252000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>250700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>252000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>273900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>196600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>197700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>492600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>228800</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,39 +2069,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>119852800</v>
+        <v>149983100</v>
       </c>
       <c r="E54" s="3">
+        <v>121532800</v>
+      </c>
+      <c r="F54" s="3">
         <v>109883700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>107145000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>107734900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>91442400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>75221600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>63998700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>63754300</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,188 +2135,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>93190300</v>
+        <v>114224000</v>
       </c>
       <c r="E57" s="3">
+        <v>92592600</v>
+      </c>
+      <c r="F57" s="3">
         <v>85769000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>87493100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>87974800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>74440700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>60195700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>52422900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>51888000</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7802400</v>
+      </c>
+      <c r="E58" s="3">
         <v>6369100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6437400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3761900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2071500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2375000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1501100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1170700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1491400</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3575200</v>
+        <v>6995000</v>
       </c>
       <c r="E59" s="3">
+        <v>6221100</v>
+      </c>
+      <c r="F59" s="3">
         <v>3008900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3055500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3218000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2955700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2517000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1955700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1956300</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>103551600</v>
+        <v>129332500</v>
       </c>
       <c r="E60" s="3">
+        <v>105465000</v>
+      </c>
+      <c r="F60" s="3">
         <v>95633000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>94676800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>93738200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>80184800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>64515800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55799500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>55571300</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5860000</v>
+        <v>8390200</v>
       </c>
       <c r="E61" s="3">
+        <v>5767500</v>
+      </c>
+      <c r="F61" s="3">
         <v>4616900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3818800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5054800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3381900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3801000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2268000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2201500</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>744900</v>
+        <v>504400</v>
       </c>
       <c r="E62" s="3">
+        <v>644900</v>
+      </c>
+      <c r="F62" s="3">
         <v>840000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>711300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>886400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>766500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1087400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>991900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1077600</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,39 +2429,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>110769300</v>
+        <v>138897400</v>
       </c>
       <c r="E66" s="3">
+        <v>112449300</v>
+      </c>
+      <c r="F66" s="3">
         <v>101764900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>99899300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100614100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>85306100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>69665000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>59270800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>59123600</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,39 +2609,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9141200</v>
+      </c>
+      <c r="E72" s="3">
         <v>7314100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6528800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5798100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5674400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4672100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4080400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3384100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3241000</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,39 +2741,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10605100</v>
+      </c>
+      <c r="E76" s="3">
         <v>8667300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7906600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7075600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6907100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5966800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5407500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4589300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4494100</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1298600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1175400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1164000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>993900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>891600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>303300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>492700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>402700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>362800</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>70000</v>
+        <v>98200</v>
       </c>
       <c r="E83" s="3">
-        <v>60800</v>
+        <v>101300</v>
       </c>
       <c r="F83" s="3">
+        <v>173000</v>
+      </c>
+      <c r="G83" s="3">
         <v>164700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>173000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>152700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>134900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>113500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>124800</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2092500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1162200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>559000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-269000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1433000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2193900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1664100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>39100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1671800</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,38 +3142,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-219900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-229500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-331500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-302600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-314100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-260000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-171400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-126600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-150100</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10155900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7333000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8347800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8036000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8199500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5959300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2795800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5961400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1959400</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,38 +3289,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>513800</v>
+      </c>
+      <c r="E96" s="3">
         <v>316600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>290700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>175500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>46300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>15200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>73800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>31600</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,97 +3418,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9078100</v>
+      </c>
+      <c r="E100" s="3">
         <v>9830600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3519600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9581900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12303000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8972300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2423200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4207400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-28200</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-85300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-25800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>191700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-66900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-78100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-67500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>52400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>11200</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>929400</v>
+      </c>
+      <c r="E102" s="3">
         <v>3634000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4280700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1468600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5469600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5128800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1224100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1662500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-304600</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
